--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -580,27 +580,41 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  O Сеттинг — ключевые слова через запятую (например «фэнтези, детектив»),</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">      каждое слово превращается в отдельный тег на карточке игры. Необязательно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Руками там ничего заполнять не нужно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>Руками там ничего заполнять не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -617,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,6 +648,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,6 +720,11 @@
       <c r="N1" s="2" t="inlineStr">
         <is>
           <t>BGG</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Сеттинг</t>
         </is>
       </c>
     </row>
@@ -749,6 +769,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -791,6 +812,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -833,6 +855,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -867,6 +890,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -909,6 +933,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -951,6 +976,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -985,6 +1011,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1019,6 +1046,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1053,6 +1081,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1087,6 +1116,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1121,6 +1151,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1155,6 +1186,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1189,6 +1221,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1223,6 +1256,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1265,6 +1299,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1299,6 +1334,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -594,27 +594,41 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P Картинка — прямая ссылка на изображение игры (обложка коробки и т.п.),</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">      покажется на карточке анонса на сайте. Необязательно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Руками там ничего заполнять не нужно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t>Руками там ничего заполнять не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -631,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -649,6 +663,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,6 +740,11 @@
       <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Сеттинг</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Картинка</t>
         </is>
       </c>
     </row>
@@ -770,6 +790,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -813,6 +834,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -856,6 +878,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -891,6 +914,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -934,6 +958,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -977,6 +1002,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1012,6 +1038,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1047,6 +1074,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1082,6 +1110,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1117,6 +1146,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1152,6 +1182,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1187,6 +1218,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1222,6 +1254,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1257,6 +1290,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1300,6 +1334,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1335,6 +1370,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -450,9 +450,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -607,9 +605,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -624,9 +620,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -762,7 +756,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Корона из пепла</t>
@@ -778,19 +771,11 @@
           <t>Настя</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Набрано</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -806,7 +791,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>База Шеклтон</t>
@@ -822,19 +806,11 @@
           <t>Даша</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Набрано</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -850,7 +826,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>НРИ</t>
@@ -866,39 +841,26 @@
           <t>Влад</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Набор открыт</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
         <v>46238</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Descent</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Непубличное</t>
@@ -909,12 +871,6 @@
           <t>Участники: Влад, Таня, Дима</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -930,7 +886,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Таверна Красный дракон</t>
@@ -946,19 +901,11 @@
           <t>Даша</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Набор открыт</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -974,7 +921,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>МПК+Брасс Бирмингем</t>
@@ -990,307 +936,211 @@
           <t>Даша</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Набор открыт</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
         <v>46244</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Манчикин Ктулху</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
         <v>46245</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>5 племен</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Дима</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
         <v>46248</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>КУА для новичков</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
         <v>46249</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Древний ужас</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
         <v>46251</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Тайные послания только Аркхэм + рол энд райт по Аркхэму</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
         <v>46254</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Нечто</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>КУА для новичков</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
         <v>46256</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Эпический режим КУА</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1306,7 +1156,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Обольщение</t>
@@ -1322,55 +1171,36 @@
           <t>Настя</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Unmatched турнир</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Дима</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1388,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1398,6 +1228,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1436,6 +1267,11 @@
           <t>Статус</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -620,9 +620,16 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D Жанр — например «Евро», «Пати», «Кооператив», «НРИ». Можно оставить пустым.</t>
+          <t xml:space="preserve">  D Жанр — можно несколько через запятую (например «Стратегия, Евро», «Абстрактная», «Контроль территории», «Кооперативная»). Можно оставить пустым.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  I Статус — один из: Набор открыт / Набрано / Отменено / Непубличное / Черновик.</t>
+          <t xml:space="preserve">  I Статус — один из: Набор открыт / Набрано / Отменено / Запланировано / Непубличное / Черновик.</t>
         </is>
       </c>
     </row>
@@ -538,98 +538,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Непубличное и Черновик на сайте не показываются — используйте для внутренних заметок.</t>
+          <t xml:space="preserve">      Запланировано — видно только организатору (по email в колонке Q) и тем, кто знает секретное слово амбассадора, пока не будет опубликовано.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  J Комментарий — любая дополнительная информация, необязательно.</t>
+          <t xml:space="preserve">      Непубличное и Черновик на сайте не показываются — используйте для внутренних заметок.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K Сложность — Лёгкая / Средняя / Сложная. Необязательно.</t>
+          <t xml:space="preserve">  J Комментарий — любая дополнительная информация, необязательно.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  L Макс. время игры (мин) — время партии при максимальном числе участников. Необязательно.</t>
+          <t xml:space="preserve">  K Сложность — Лёгкая / Средняя / Сложная. Необязательно.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  M Тесера — ссылка на страницу игры на tesera.ru. Необязательно.</t>
+          <t xml:space="preserve">  L Макс. время игры (мин) — время партии при максимальном числе участников. Необязательно.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  N BGG — ссылка на страницу игры на boardgamegeek.com. Необязательно.</t>
+          <t xml:space="preserve">  M Тесера — ссылка на страницу игры на tesera.ru. Необязательно.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  O Сеттинг — ключевые слова через запятую (например «фэнтези, детектив»),</t>
+          <t xml:space="preserve">  N BGG — ссылка на страницу игры на boardgamegeek.com. Необязательно.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">      каждое слово превращается в отдельный тег на карточке игры. Необязательно.</t>
+          <t xml:space="preserve">  O Сеттинг — ключевые слова через запятую (например «фэнтези, детектив»),</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  P Картинка — прямая ссылка на изображение игры (обложка коробки и т.п.),</t>
+          <t xml:space="preserve">      каждое слово превращается в отдельный тег на карточке игры. Необязательно.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">  P Картинка — прямая ссылка на изображение игры (обложка коробки и т.п.),</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t xml:space="preserve">      покажется на карточке анонса на сайте. Необязательно.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Руками там ничего заполнять не нужно.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  Q Email организатора — обязательна для игр, добавленных через форму сайта; нужна для подсказки при наведении на организатора и чтобы можно было опубликовать запланированную игру.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Руками там ничего заполнять не нужно.</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" t="inlineStr">
+        <is>
+          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -646,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -665,6 +679,7 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,6 +763,11 @@
           <t>Картинка</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Email организатора</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1212,7 +1232,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Набор открыт,Набрано,Отменено,Непубличное,Черновик"</formula1>
+      <formula1>"Набор открыт,Набрано,Отменено,Запланировано,Непубличное,Черновик"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мероприятия" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Записи" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аккаунты" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -531,14 +532,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Публично на сайте видны только: Набор открыт, Набрано, Отменено.</t>
+          <t xml:space="preserve">      Публично на сайте видны только: Набор открыт, Набрано, Отменено (и то, если мероприятие не «Закрытое» — см. колонку R).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Запланировано — видно только организатору (по email в колонке Q) и тем, кто знает секретное слово амбассадора, пока не будет опубликовано.</t>
+          <t xml:space="preserve">      Запланировано — видно только организатору (по email в колонке Q) и тем, у кого в листе «Аккаунты» стоит роль «Амбассадор», пока не будет опубликовано.</t>
         </is>
       </c>
     </row>
@@ -615,35 +616,148 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Q Email организатора — обязательна для игр, добавленных через форму сайта; нужна для подсказки при наведении на организатора и чтобы можно было опубликовать запланированную игру.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  Q Email организатора — обязательна для игр, добавленных через форму сайта; нужна для подсказки при наведении на организатора, чтобы можно было опубликовать запланированную игру, и чтобы сайт узнавал организатора при входе через «это вы».</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  R Закрытое — ДА / НЕТ (или пусто = НЕТ). «ДА» — мероприятие скрыто из общего списка на сайте, как и «Запланировано»: его видят только организатор, амбассадоры и те, кого организатор сам вписал участниками при создании (списком, через форму сайта). Самостоятельно записаться на такое мероприятие через сайт нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Руками там ничего заполнять не нужно.</t>
+          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Руками там ничего заполнять не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>редактирования уже существующей роли в колонке D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -660,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -680,6 +794,7 @@
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -768,6 +883,11 @@
           <t>Email организатора</t>
         </is>
       </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Закрытое</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -803,6 +923,11 @@
           <t>Набрано</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -838,6 +963,11 @@
           <t>Набрано</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -873,6 +1003,11 @@
           <t>Набор открыт</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -898,6 +1033,11 @@
           <t>Участники: Влад, Таня, Дима</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -933,6 +1073,11 @@
           <t>Набор открыт</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -968,6 +1113,11 @@
           <t>Набор открыт</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -993,6 +1143,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1018,6 +1173,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1043,6 +1203,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1068,6 +1233,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1093,6 +1263,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1118,6 +1293,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1143,6 +1323,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1168,6 +1353,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1203,6 +1393,11 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1228,11 +1423,19 @@
           <t>Черновик</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Набор открыт,Набрано,Отменено,Запланировано,Непубличное,Черновик"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ДА,НЕТ"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1303,4 +1506,57 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>PIN</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Дата регистрации</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Участник,Амбассадор"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -627,137 +627,172 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S Занято организатором — число (по умолчанию 0). Организатор может через сайт вручную</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
+          <t xml:space="preserve">      отметить +1/-1 место как занятое, без имени/почты (например, если кто-то</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Руками там ничего заполнять не нужно.</t>
+          <t xml:space="preserve">      договорился вне сайта). Складывается с обычными именными записями при подсчёте</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">      «занято из максимума» — руками эту колонку обычно трогать не нужно, ей управляет</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      кнопка +/- на карточке мероприятия на сайте (видна только организатору).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
+          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
+          <t>Руками там ничего заполнять не нужно.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
-        </is>
-      </c>
-    </row>
+          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
+          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
+          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
+          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
+          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
+          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>редактирования уже существующей роли в колонке D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
       <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>редактирования уже существующей роли в колонке D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -774,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -795,6 +830,7 @@
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -888,6 +924,11 @@
           <t>Закрытое</t>
         </is>
       </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Занято организатором</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -928,6 +969,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -968,6 +1012,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1008,6 +1055,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1038,6 +1088,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1078,6 +1131,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1118,6 +1174,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1148,6 +1207,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1178,6 +1240,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1208,6 +1273,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1238,6 +1306,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1268,6 +1339,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1298,6 +1372,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1328,6 +1405,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1358,6 +1438,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1398,6 +1481,9 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1427,6 +1513,9 @@
         <is>
           <t>НЕТ</t>
         </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -662,137 +661,172 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  T Тип — Игра или Событие (пусто = Игра, для старых строк).</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
+          <t xml:space="preserve">      Игра — обычный анонс с записью, как раньше.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Руками там ничего заполнять не нужно.</t>
+          <t xml:space="preserve">      Событие — просто отметка «что-то будет», без записи и без счётчика мест;</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">      на сайте у него нет ни блока участников, ни кнопки «Записаться»/«Проявить</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      интерес» — только описание (в колонке E), где, когда и город.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
+          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
+          <t>Руками там ничего заполнять не нужно.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
-        </is>
-      </c>
-    </row>
+          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
+          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
+          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
+          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
+          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
+          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>редактирования уже существующей роли в колонке D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
+          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+        </is>
+      </c>
+    </row>
     <row r="54">
       <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>редактирования уже существующей роли в колонке D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -809,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -831,6 +865,7 @@
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -929,6 +964,11 @@
           <t>Занято организатором</t>
         </is>
       </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -972,6 +1012,11 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1015,6 +1060,11 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1058,6 +1108,11 @@
       <c r="S4" t="n">
         <v>0</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1091,6 +1146,11 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1134,6 +1194,11 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1177,6 +1242,11 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1210,6 +1280,11 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1243,6 +1318,11 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1276,6 +1356,11 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1309,6 +1394,11 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1342,6 +1432,11 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1375,6 +1470,11 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1408,6 +1508,11 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1441,6 +1546,11 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1484,6 +1594,11 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1517,14 +1632,22 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Набор открыт,Набрано,Отменено,Запланировано,Непубличное,Черновик"</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ДА,НЕТ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Игра,Событие"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мероприятия" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Записи" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аккаунты" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заявки" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заявки_голоса" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +41,7 @@
       <color rgb="FFFFC800"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +52,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF202632"/>
         <bgColor rgb="FF202632"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF202632"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -73,6 +80,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -696,137 +706,243 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  U Игры события — техническая колонка для «Событий»: список прикреплённых настольных</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
+          <t xml:space="preserve">      игр (название||жанр||сложность||время||сеттинг||тесера||bgg||картинка на строку,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Руками там ничего заполнять не нужно.</t>
+          <t xml:space="preserve">      разделены переносом строки). Заполняется формой анонса сама — руками лучше не</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
+          <t xml:space="preserve">      трогать, для «Игра» всегда остаётся пустой.</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
+          <t>Лист «Записи» — сюда сайт сам записывает, кто на что записался и кто отменил запись.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
+          <t>Руками там ничего заполнять не нужно.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
+          <t>В колонке «Статус» там может быть Записан / Отменено / Интересуюсь (последнее — от кнопки «Проявить интерес» на сайте, не занимает мест).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
+          <t>Лист «Аккаунты» — здесь сайт хранит, кто есть кто: email, имя, 4-значный код (PIN) и роль.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
+          <t xml:space="preserve">  A Email — почта человека (уникальный ключ; регистр не важен).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
+          <t xml:space="preserve">  B Имя — как человек в последний раз представился на сайте (сайт обновляет это поле сам).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
+          <t xml:space="preserve">  C PIN — 4-значный код, который человек сам придумал при первом входе под этой почтой.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
+          <t xml:space="preserve">      Хранится как текст (важно для кодов вроде «0512» — с ведущим нулём).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
+          <t xml:space="preserve">  D Роль — Участник или Амбассадор. Пусто = Участник.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+          <t xml:space="preserve">      ЭТУ КОЛОНКУ МОЖНО МЕНЯТЬ ТОЛЬКО ЗДЕСЬ, ВРУЧНУЮ. С сайта её нельзя ни поставить,</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+          <t xml:space="preserve">      ни даже увидеть — там просто нет такой возможности. Чтобы сделать кого-то</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+          <t xml:space="preserve">      амбассадором, найдите его строку по email и впишите (или выберите из списка)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+          <t xml:space="preserve">      «Амбассадор» в колонке D. Амбассадор видит ВСЕ запланированные и ВСЕ закрытые</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>редактирования уже существующей роли в колонке D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
+          <t xml:space="preserve">      мероприятия всех организаторов (не только свои) и может публиковать любое из них.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E Дата регистрации — когда почта впервые появилась на сайте. Просто для справки.</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
       <c r="A59" t="inlineStr">
+        <is>
+          <t>Строки в этот лист сайт добавляет и обновляет сам (при первом «это вы» и при каждом</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>повторном подтверждении кода) — руками добавлять новые строки не нужно, кроме</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>редактирования уже существующей роли в колонке D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Лист «Заявки» — каталог настольных игр для вкладки «Приём заявок» на сайте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Пополняется ТОЛЬКО вручную (вами или амбассадорами) — сайт этот лист только читает</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>и считает голоса, сам в него ничего не добавляет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A Игра — название игры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B Офис — в каком офисе/офисах она уже доступна, через запятую (например</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      «Москва, Санкт-Петербург»). Можно оставить пустым, если нигде ещё нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C Ссылка на BGG — страница игры на boardgamegeek.com. Необязательно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Лист «Заявки_голоса» — сюда сайт сам записывает, кто за какую игру поставил</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>плюсик (и кто его снял). Руками ничего заполнять не нужно. Один плюсик на игру</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>на человека, но игр поддержать можно сколько угодно — учитывается последний</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>статус («Голос» или «Отмена») на пару (игра, email), так же, как и в «Записи».</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -843,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -866,6 +982,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -967,6 +1084,11 @@
       <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Тип</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Игры события</t>
         </is>
       </c>
     </row>
@@ -1771,4 +1893,88 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Офис</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Ссылка на BGG</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -891,27 +891,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  B Офис — в каком офисе/офисах она уже доступна, через запятую (например</t>
+          <t xml:space="preserve">  B Доступность в офисе — в каком офисе/офисах уже есть, через точку с</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">      «Москва, Санкт-Петербург»). Можно оставить пустым, если нигде ещё нет.</t>
+          <t xml:space="preserve">      запятой (например «Москва; Рязань»). Запятая внутри одного офиса не страшна.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  C Ссылка на BGG — страница игры на boardgamegeek.com. Необязательно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-    </row>
+          <t xml:space="preserve">  C Возможность сыграть на BGA — чекбокс (да/нет), ставится вручную.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
@@ -940,7 +938,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
@@ -1906,7 +1903,7 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1917,12 +1914,12 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Доступность в офисе</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Ссылка на BGG</t>
+          <t>Возможность сыграть на BGA</t>
         </is>
       </c>
     </row>

--- a/Настолки_Билайн_данные.xlsx
+++ b/Настолки_Билайн_данные.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -909,37 +909,45 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Лист «Заявки_голоса» — сюда сайт сам записывает, кто за какую игру поставил</t>
-        </is>
-      </c>
-    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D Амбассадор(ы), кто может провести — свободный текст, несколько через ";", необязательно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>плюсик (и кто его снял). Руками ничего заполнять не нужно. Один плюсик на игру</t>
+          <t>Лист «Заявки_голоса» — сюда сайт сам записывает, кто за какую игру поставил</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>на человека, но игр поддержать можно сколько угодно — учитывается последний</t>
+          <t>плюсик (и кто его снял). Руками ничего заполнять не нужно. Один плюсик на игру</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>на человека, но игр поддержать можно сколько угодно — учитывается последний</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>статус («Голос» или «Отмена») на пару (игра, email), так же, как и в «Записи».</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Подробная пошаговая инструкция по установке сайта — в файле SETUP.md рядом с сайтом.</t>
         </is>
@@ -1898,12 +1906,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1920,6 +1929,11 @@
       <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Возможность сыграть на BGA</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Амбассадор(ы), кто может провести</t>
         </is>
       </c>
     </row>
